--- a/samples/Trial_Balance_UK_Aug-26.xlsx
+++ b/samples/Trial_Balance_UK_Aug-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>54870.41</v>
+        <v>286150.97</v>
       </c>
     </row>
     <row r="8">
@@ -464,7 +464,7 @@
         <v>Cash</v>
       </c>
       <c r="D8">
-        <v>121.9</v>
+        <v>110.01</v>
       </c>
     </row>
     <row r="9">
@@ -478,7 +478,7 @@
         <v>Accounts Receivable</v>
       </c>
       <c r="D9">
-        <v>39698.92</v>
+        <v>37176.85</v>
       </c>
     </row>
     <row r="10">
@@ -492,7 +492,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D10">
-        <v>2353.66</v>
+        <v>2485.51</v>
       </c>
     </row>
     <row r="11">
@@ -506,7 +506,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D11">
-        <v>2124.4</v>
+        <v>1952.6</v>
       </c>
     </row>
     <row r="12">
@@ -520,7 +520,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D12">
-        <v>4604.91</v>
+        <v>4571.1</v>
       </c>
     </row>
     <row r="13">
@@ -534,7 +534,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D13">
-        <v>19991.83</v>
+        <v>19267.04</v>
       </c>
     </row>
     <row r="14">
@@ -548,7 +548,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D14">
-        <v>-7607.95</v>
+        <v>-7124.61</v>
       </c>
     </row>
     <row r="15">
@@ -562,7 +562,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D15">
-        <v>1205.6</v>
+        <v>1196.75</v>
       </c>
     </row>
     <row r="16">
@@ -576,7 +576,7 @@
         <v>Accounts Payable</v>
       </c>
       <c r="D16">
-        <v>-11582.54</v>
+        <v>-10950</v>
       </c>
     </row>
     <row r="17">
@@ -590,7 +590,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D17">
-        <v>-6165.48</v>
+        <v>-5614.87</v>
       </c>
     </row>
     <row r="18">
@@ -604,7 +604,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D18">
-        <v>-3400.4</v>
+        <v>-2700.35</v>
       </c>
     </row>
     <row r="19">
@@ -618,7 +618,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D19">
-        <v>-2272.15</v>
+        <v>-2168.72</v>
       </c>
     </row>
     <row r="20">
@@ -632,7 +632,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D20">
-        <v>-3562.9</v>
+        <v>-81884.34</v>
       </c>
     </row>
     <row r="21">
@@ -646,7 +646,7 @@
         <v>Equity</v>
       </c>
       <c r="D21">
-        <v>-47637</v>
+        <v>-150000</v>
       </c>
     </row>
     <row r="22">
@@ -660,7 +660,7 @@
         <v>Equity</v>
       </c>
       <c r="D22">
-        <v>-25431.68</v>
+        <v>-50000</v>
       </c>
     </row>
     <row r="23">
@@ -674,7 +674,7 @@
         <v>Equity</v>
       </c>
       <c r="D23">
-        <v>-13063.85</v>
+        <v>-12967.94</v>
       </c>
     </row>
     <row r="24">
@@ -688,7 +688,7 @@
         <v>Income</v>
       </c>
       <c r="D24">
-        <v>-120005.11</v>
+        <v>-155384.6</v>
       </c>
     </row>
     <row r="25">
@@ -702,7 +702,7 @@
         <v>Other Income</v>
       </c>
       <c r="D25">
-        <v>-755</v>
+        <v>-599.57</v>
       </c>
     </row>
     <row r="26">
@@ -716,7 +716,7 @@
         <v>Cost Of Goods Sold</v>
       </c>
       <c r="D26">
-        <v>43501.11</v>
+        <v>34545.39</v>
       </c>
     </row>
     <row r="27">
@@ -730,7 +730,7 @@
         <v>Expense</v>
       </c>
       <c r="D27">
-        <v>37481.31</v>
+        <v>29764.91</v>
       </c>
     </row>
     <row r="28">
@@ -744,7 +744,7 @@
         <v>Expense</v>
       </c>
       <c r="D28">
-        <v>3486.43</v>
+        <v>2768.67</v>
       </c>
     </row>
     <row r="29">
@@ -758,7 +758,7 @@
         <v>Expense</v>
       </c>
       <c r="D29">
-        <v>4922.49</v>
+        <v>3909.08</v>
       </c>
     </row>
     <row r="30">
@@ -772,7 +772,7 @@
         <v>Expense</v>
       </c>
       <c r="D30">
-        <v>3831.5</v>
+        <v>3042.7</v>
       </c>
     </row>
     <row r="31">
@@ -786,7 +786,7 @@
         <v>Expense</v>
       </c>
       <c r="D31">
-        <v>118.5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32">
@@ -800,7 +800,7 @@
         <v>Expense</v>
       </c>
       <c r="D32">
-        <v>6293.06</v>
+        <v>4997.49</v>
       </c>
     </row>
     <row r="33">
@@ -814,7 +814,7 @@
         <v>Expense</v>
       </c>
       <c r="D33">
-        <v>2101.87</v>
+        <v>1669.15</v>
       </c>
     </row>
     <row r="34">
@@ -828,7 +828,7 @@
         <v>Expense</v>
       </c>
       <c r="D34">
-        <v>10171.25</v>
+        <v>42034.9</v>
       </c>
     </row>
     <row r="35">
@@ -842,7 +842,7 @@
         <v>Expense</v>
       </c>
       <c r="D35">
-        <v>4604.91</v>
+        <v>3656.88</v>
       </c>
     </row>
     <row r="36">

--- a/samples/Trial_Balance_UK_Aug-26.xlsx
+++ b/samples/Trial_Balance_UK_Aug-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>286150.97</v>
+        <v>395183.03</v>
       </c>
     </row>
     <row r="8">
@@ -674,7 +674,7 @@
         <v>Equity</v>
       </c>
       <c r="D23">
-        <v>-12967.94</v>
+        <v>-122000</v>
       </c>
     </row>
     <row r="24">
@@ -688,7 +688,7 @@
         <v>Income</v>
       </c>
       <c r="D24">
-        <v>-155384.6</v>
+        <v>-93349.96</v>
       </c>
     </row>
     <row r="25">
@@ -702,7 +702,7 @@
         <v>Other Income</v>
       </c>
       <c r="D25">
-        <v>-599.57</v>
+        <v>-157.78</v>
       </c>
     </row>
     <row r="26">
@@ -716,7 +716,7 @@
         <v>Cost Of Goods Sold</v>
       </c>
       <c r="D26">
-        <v>34545.39</v>
+        <v>8620.62</v>
       </c>
     </row>
     <row r="27">
@@ -730,7 +730,7 @@
         <v>Expense</v>
       </c>
       <c r="D27">
-        <v>29764.91</v>
+        <v>7449.08</v>
       </c>
     </row>
     <row r="28">
@@ -744,7 +744,7 @@
         <v>Expense</v>
       </c>
       <c r="D28">
-        <v>2768.67</v>
+        <v>692.17</v>
       </c>
     </row>
     <row r="29">
@@ -758,7 +758,7 @@
         <v>Expense</v>
       </c>
       <c r="D29">
-        <v>3909.08</v>
+        <v>977.27</v>
       </c>
     </row>
     <row r="30">
@@ -772,7 +772,7 @@
         <v>Expense</v>
       </c>
       <c r="D30">
-        <v>3042.7</v>
+        <v>752.83</v>
       </c>
     </row>
     <row r="31">
@@ -786,7 +786,7 @@
         <v>Expense</v>
       </c>
       <c r="D31">
-        <v>95</v>
+        <v>900</v>
       </c>
     </row>
     <row r="32">
@@ -800,7 +800,7 @@
         <v>Expense</v>
       </c>
       <c r="D32">
-        <v>4997.49</v>
+        <v>1257.23</v>
       </c>
     </row>
     <row r="33">
@@ -814,7 +814,7 @@
         <v>Expense</v>
       </c>
       <c r="D33">
-        <v>1669.15</v>
+        <v>409.42</v>
       </c>
     </row>
     <row r="34">
@@ -842,7 +842,7 @@
         <v>Expense</v>
       </c>
       <c r="D35">
-        <v>3656.88</v>
+        <v>914.22</v>
       </c>
     </row>
     <row r="36">

--- a/samples/Trial_Balance_UK_Aug-26.xlsx
+++ b/samples/Trial_Balance_UK_Aug-26.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D35"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>395183.03</v>
+        <v>430693.67</v>
       </c>
     </row>
     <row r="8">
@@ -464,7 +464,7 @@
         <v>Cash</v>
       </c>
       <c r="D8">
-        <v>110.01</v>
+        <v>104.79</v>
       </c>
     </row>
     <row r="9">
@@ -478,7 +478,7 @@
         <v>Accounts Receivable</v>
       </c>
       <c r="D9">
-        <v>37176.85</v>
+        <v>35413.3</v>
       </c>
     </row>
     <row r="10">
@@ -492,7 +492,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D10">
-        <v>2485.51</v>
+        <v>2367.59</v>
       </c>
     </row>
     <row r="11">
@@ -506,7 +506,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D11">
-        <v>1952.6</v>
+        <v>1859.97</v>
       </c>
     </row>
     <row r="12">
@@ -520,7 +520,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D12">
-        <v>4571.1</v>
+        <v>4354.27</v>
       </c>
     </row>
     <row r="13">
@@ -534,7 +534,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D13">
-        <v>19267.04</v>
+        <v>18353.06</v>
       </c>
     </row>
     <row r="14">
@@ -548,7 +548,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D14">
-        <v>-7124.61</v>
+        <v>-6786.64</v>
       </c>
     </row>
     <row r="15">
@@ -562,7 +562,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D15">
-        <v>1196.75</v>
+        <v>1139.99</v>
       </c>
     </row>
     <row r="16">
@@ -576,7 +576,7 @@
         <v>Accounts Payable</v>
       </c>
       <c r="D16">
-        <v>-10950</v>
+        <v>-48013.39</v>
       </c>
     </row>
     <row r="17">
@@ -590,7 +590,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D17">
-        <v>-5614.87</v>
+        <v>-5348.52</v>
       </c>
     </row>
     <row r="18">
@@ -604,7 +604,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D18">
-        <v>-2700.35</v>
+        <v>-2572.25</v>
       </c>
     </row>
     <row r="19">
@@ -618,7 +618,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D19">
-        <v>-2168.72</v>
+        <v>-2065.84</v>
       </c>
     </row>
     <row r="20">
@@ -632,7 +632,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D20">
-        <v>-81884.34</v>
+        <v>-78000</v>
       </c>
     </row>
     <row r="21">
@@ -646,216 +646,202 @@
         <v>Equity</v>
       </c>
       <c r="D21">
-        <v>-150000</v>
+        <v>-200000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="B22" t="str">
-        <v>Securities Premium</v>
+        <v>Retained Earnings</v>
       </c>
       <c r="C22" t="str">
         <v>Equity</v>
       </c>
       <c r="D22">
-        <v>-50000</v>
+        <v>-122000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>3200</v>
+        <v>4001</v>
       </c>
       <c r="B23" t="str">
-        <v>Retained Earnings</v>
+        <v>Consulting Revenue</v>
       </c>
       <c r="C23" t="str">
-        <v>Equity</v>
+        <v>Income</v>
       </c>
       <c r="D23">
-        <v>-122000</v>
+        <v>-90322.89</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>4001</v>
+        <v>4500</v>
       </c>
       <c r="B24" t="str">
-        <v>Consulting Revenue</v>
+        <v>Interest Income</v>
       </c>
       <c r="C24" t="str">
-        <v>Income</v>
+        <v>Other Income</v>
       </c>
       <c r="D24">
-        <v>-93349.96</v>
+        <v>-150.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>4500</v>
+        <v>5001</v>
       </c>
       <c r="B25" t="str">
-        <v>Interest Income</v>
+        <v>Cost of Services</v>
       </c>
       <c r="C25" t="str">
-        <v>Other Income</v>
+        <v>Cost Of Goods Sold</v>
       </c>
       <c r="D25">
-        <v>-157.78</v>
+        <v>8211.69</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>5001</v>
+        <v>6001</v>
       </c>
       <c r="B26" t="str">
-        <v>Cost of Services</v>
+        <v>Salaries and Wages</v>
       </c>
       <c r="C26" t="str">
-        <v>Cost Of Goods Sold</v>
+        <v>Expense</v>
       </c>
       <c r="D26">
-        <v>8620.62</v>
+        <v>7095.71</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>6001</v>
+        <v>6100</v>
       </c>
       <c r="B27" t="str">
-        <v>Salaries and Wages</v>
+        <v>Travel and Conveyance</v>
       </c>
       <c r="C27" t="str">
         <v>Expense</v>
       </c>
       <c r="D27">
-        <v>7449.08</v>
+        <v>659.26</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>6100</v>
+        <v>6200</v>
       </c>
       <c r="B28" t="str">
-        <v>Travel and Conveyance</v>
+        <v>Professional Fees</v>
       </c>
       <c r="C28" t="str">
         <v>Expense</v>
       </c>
       <c r="D28">
-        <v>692.17</v>
+        <v>930.98</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>6200</v>
+        <v>6300</v>
       </c>
       <c r="B29" t="str">
-        <v>Professional Fees</v>
+        <v>Software Subscriptions</v>
       </c>
       <c r="C29" t="str">
         <v>Expense</v>
       </c>
       <c r="D29">
-        <v>977.27</v>
+        <v>717.11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>6300</v>
+        <v>6390</v>
       </c>
       <c r="B30" t="str">
-        <v>Software Subscriptions</v>
+        <v>Bank Charges</v>
       </c>
       <c r="C30" t="str">
         <v>Expense</v>
       </c>
       <c r="D30">
-        <v>752.83</v>
+        <v>900</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>6390</v>
+        <v>6400</v>
       </c>
       <c r="B31" t="str">
-        <v>Bank Charges</v>
+        <v>Rent</v>
       </c>
       <c r="C31" t="str">
         <v>Expense</v>
       </c>
       <c r="D31">
-        <v>900</v>
+        <v>1197.59</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="B32" t="str">
-        <v>Rent</v>
+        <v>Depreciation</v>
       </c>
       <c r="C32" t="str">
         <v>Expense</v>
       </c>
       <c r="D32">
-        <v>1257.23</v>
+        <v>390</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>6500</v>
+        <v>6600</v>
       </c>
       <c r="B33" t="str">
-        <v>Depreciation</v>
+        <v>IC Service Charges - India</v>
       </c>
       <c r="C33" t="str">
         <v>Expense</v>
       </c>
       <c r="D33">
-        <v>409.42</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>6600</v>
+        <v>6900</v>
       </c>
       <c r="B34" t="str">
-        <v>IC Service Charges - India</v>
+        <v>Income Tax Expense</v>
       </c>
       <c r="C34" t="str">
         <v>Expense</v>
       </c>
       <c r="D34">
-        <v>42034.9</v>
+        <v>870.85</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
-        <v>6900</v>
-      </c>
       <c r="B35" t="str">
-        <v>Income Tax Expense</v>
-      </c>
-      <c r="C35" t="str">
-        <v>Expense</v>
+        <v>Total</v>
       </c>
       <c r="D35">
-        <v>914.22</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="str">
-        <v>Total</v>
-      </c>
-      <c r="D36">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D35"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/Trial_Balance_UK_Aug-26.xlsx
+++ b/samples/Trial_Balance_UK_Aug-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>430693.67</v>
+        <v>262714.07</v>
       </c>
     </row>
     <row r="8">
@@ -492,7 +492,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D10">
-        <v>2367.59</v>
+        <v>2367.6</v>
       </c>
     </row>
     <row r="11">
@@ -520,7 +520,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D12">
-        <v>4354.27</v>
+        <v>4354.26</v>
       </c>
     </row>
     <row r="13">
@@ -534,7 +534,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D13">
-        <v>18353.06</v>
+        <v>18353.07</v>
       </c>
     </row>
     <row r="14">
@@ -562,7 +562,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D15">
-        <v>1139.99</v>
+        <v>1139.98</v>
       </c>
     </row>
     <row r="16">
@@ -576,7 +576,7 @@
         <v>Accounts Payable</v>
       </c>
       <c r="D16">
-        <v>-48013.39</v>
+        <v>-10430.57</v>
       </c>
     </row>
     <row r="17">
@@ -660,7 +660,7 @@
         <v>Equity</v>
       </c>
       <c r="D22">
-        <v>-122000</v>
+        <v>-59246.47</v>
       </c>
     </row>
     <row r="23">
@@ -674,7 +674,7 @@
         <v>Income</v>
       </c>
       <c r="D23">
-        <v>-90322.89</v>
+        <v>-22679.64</v>
       </c>
     </row>
     <row r="24">
@@ -702,7 +702,7 @@
         <v>Cost Of Goods Sold</v>
       </c>
       <c r="D25">
-        <v>8211.69</v>
+        <v>8211.68</v>
       </c>
     </row>
     <row r="26">
@@ -716,7 +716,7 @@
         <v>Expense</v>
       </c>
       <c r="D26">
-        <v>7095.71</v>
+        <v>7095.72</v>
       </c>
     </row>
     <row r="27">
@@ -730,7 +730,7 @@
         <v>Expense</v>
       </c>
       <c r="D27">
-        <v>659.26</v>
+        <v>659.33</v>
       </c>
     </row>
     <row r="28">
@@ -744,7 +744,7 @@
         <v>Expense</v>
       </c>
       <c r="D28">
-        <v>930.98</v>
+        <v>930.91</v>
       </c>
     </row>
     <row r="29">
@@ -758,7 +758,7 @@
         <v>Expense</v>
       </c>
       <c r="D29">
-        <v>717.11</v>
+        <v>717.12</v>
       </c>
     </row>
     <row r="30">
@@ -800,7 +800,7 @@
         <v>Expense</v>
       </c>
       <c r="D32">
-        <v>390</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="33">
